--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -1764,7 +1764,7 @@
         <v>38</v>
       </c>
       <c r="E18" s="3">
-        <v>1003</v>
+        <v>2003</v>
       </c>
       <c r="F18" s="3">
         <v>10</v>
@@ -1792,7 +1792,7 @@
         <v>41</v>
       </c>
       <c r="E19" s="3">
-        <v>1003</v>
+        <v>2002</v>
       </c>
       <c r="F19" s="3">
         <v>10</v>
@@ -1820,7 +1820,7 @@
         <v>43</v>
       </c>
       <c r="E20" s="3">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="F20" s="3">
         <v>10</v>
@@ -2008,7 +2008,7 @@
         <v>2003</v>
       </c>
       <c r="F27" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G27" s="3">
         <v>8</v>
@@ -2241,10 +2241,10 @@
         <v>69</v>
       </c>
       <c r="E36" s="3">
-        <v>1003</v>
+        <v>2003</v>
       </c>
       <c r="F36" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G36" s="1">
         <v>11</v>
@@ -2264,10 +2264,10 @@
         <v>71</v>
       </c>
       <c r="E37" s="3">
-        <v>1003</v>
+        <v>2002</v>
       </c>
       <c r="F37" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G37" s="1">
         <v>11</v>
@@ -2289,10 +2289,10 @@
         <v>72</v>
       </c>
       <c r="E38" s="3">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="F38" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G38" s="1">
         <v>11</v>
@@ -2315,10 +2315,10 @@
         <v>73</v>
       </c>
       <c r="E39" s="3">
-        <v>1003</v>
+        <v>2003</v>
       </c>
       <c r="F39" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G39" s="1">
         <v>12</v>
@@ -2341,10 +2341,10 @@
         <v>75</v>
       </c>
       <c r="E40" s="3">
-        <v>1003</v>
+        <v>2002</v>
       </c>
       <c r="F40" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G40" s="1">
         <v>12</v>
@@ -2367,10 +2367,10 @@
         <v>76</v>
       </c>
       <c r="E41" s="3">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="F41" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G41" s="1">
         <v>12</v>

--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="105">
   <si>
     <t>#</t>
   </si>
@@ -263,6 +263,42 @@
   </si>
   <si>
     <t>斩杀铁履</t>
+  </si>
+  <si>
+    <t>不灭护面</t>
+  </si>
+  <si>
+    <t>5E+8</t>
+  </si>
+  <si>
+    <t>不灭护手</t>
+  </si>
+  <si>
+    <t>不灭护袍</t>
+  </si>
+  <si>
+    <t>镇岳铁甲</t>
+  </si>
+  <si>
+    <t>1E+9</t>
+  </si>
+  <si>
+    <t>镇岳铁带</t>
+  </si>
+  <si>
+    <t>镇岳铁腿</t>
+  </si>
+  <si>
+    <t>冰霜项链</t>
+  </si>
+  <si>
+    <t>5E+9</t>
+  </si>
+  <si>
+    <t>冰霜戒指</t>
+  </si>
+  <si>
+    <t>冰霜银带</t>
   </si>
   <si>
     <t>幸运项链</t>
@@ -1298,7 +1334,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.125" style="1" customWidth="1"/>
@@ -2384,234 +2420,252 @@
       <c r="J41" s="1"/>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A42" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
       <c r="C42" s="3">
-        <v>211031</v>
-      </c>
-      <c r="D42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8">
+      <c r="E42" s="3">
+        <v>2003</v>
+      </c>
+      <c r="F42" s="3">
+        <v>30</v>
+      </c>
+      <c r="G42" s="1">
         <v>13</v>
       </c>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="8" t="s">
+      <c r="H42" s="9" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A43" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="I42" s="2">
+        <v>60</v>
+      </c>
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
       <c r="C43" s="3">
-        <v>211032</v>
-      </c>
-      <c r="D43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="8">
+      <c r="E43" s="3">
+        <v>2002</v>
+      </c>
+      <c r="F43" s="3">
+        <v>30</v>
+      </c>
+      <c r="G43" s="1">
         <v>13</v>
       </c>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="3"/>
-    </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A44" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="H43" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I43" s="2">
+        <v>60</v>
+      </c>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
       <c r="C44" s="3">
-        <v>211033</v>
-      </c>
-      <c r="D44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="8">
+      <c r="E44" s="3">
+        <v>2001</v>
+      </c>
+      <c r="F44" s="3">
+        <v>30</v>
+      </c>
+      <c r="G44" s="1">
         <v>13</v>
       </c>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="3"/>
-    </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A45" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="H44" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I44" s="2">
+        <v>60</v>
+      </c>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
       <c r="C45" s="3">
-        <v>211034</v>
-      </c>
-      <c r="D45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3">
+      <c r="E45" s="3">
+        <v>2003</v>
+      </c>
+      <c r="F45" s="3">
+        <v>35</v>
+      </c>
+      <c r="G45" s="1">
         <v>14</v>
       </c>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="3" t="s">
+      <c r="H45" s="9" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A46" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="I45" s="2">
+        <v>80</v>
+      </c>
+      <c r="J45" s="1"/>
+    </row>
+    <row r="46" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
       <c r="C46" s="3">
-        <v>211035</v>
-      </c>
-      <c r="D46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3">
+      <c r="E46" s="3">
+        <v>2002</v>
+      </c>
+      <c r="F46" s="3">
+        <v>35</v>
+      </c>
+      <c r="G46" s="1">
         <v>14</v>
       </c>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="3"/>
-    </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A47" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="H46" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I46" s="2">
+        <v>80</v>
+      </c>
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
       <c r="C47" s="3">
-        <v>211036</v>
-      </c>
-      <c r="D47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3">
+      <c r="E47" s="3">
+        <v>2001</v>
+      </c>
+      <c r="F47" s="3">
+        <v>35</v>
+      </c>
+      <c r="G47" s="1">
         <v>14</v>
       </c>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="3"/>
-    </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A48" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="H47" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I47" s="2">
+        <v>80</v>
+      </c>
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
       <c r="C48" s="3">
-        <v>211037</v>
-      </c>
-      <c r="D48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3">
-        <v>10</v>
-      </c>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="3" t="s">
+      <c r="E48" s="3">
+        <v>2003</v>
+      </c>
+      <c r="F48" s="3">
+        <v>40</v>
+      </c>
+      <c r="G48" s="1">
+        <v>15</v>
+      </c>
+      <c r="H48" s="9" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A49" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="I48" s="2">
+        <v>100</v>
+      </c>
+      <c r="J48" s="1"/>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
       <c r="C49" s="3">
-        <v>211038</v>
-      </c>
-      <c r="D49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3">
-        <v>10</v>
-      </c>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="3"/>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A50" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="E49" s="3">
+        <v>2002</v>
+      </c>
+      <c r="F49" s="3">
+        <v>40</v>
+      </c>
+      <c r="G49" s="1">
+        <v>15</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I49" s="2">
+        <v>100</v>
+      </c>
+      <c r="J49" s="1"/>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
       <c r="C50" s="3">
-        <v>211039</v>
-      </c>
-      <c r="D50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3">
-        <v>10</v>
-      </c>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="3"/>
-    </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A51" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C51" s="3">
-        <v>211040</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>89</v>
-      </c>
+      <c r="E50" s="3">
+        <v>2001</v>
+      </c>
+      <c r="F50" s="3">
+        <v>40</v>
+      </c>
+      <c r="G50" s="1">
+        <v>15</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I50" s="2">
+        <v>100</v>
+      </c>
+      <c r="J50" s="1"/>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="1"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
-      <c r="G51" s="3">
-        <v>3</v>
-      </c>
+      <c r="G51" s="1"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
-      <c r="J51" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="1:10">
       <c r="A52" s="3" t="s">
         <v>0</v>
       </c>
@@ -2619,19 +2673,21 @@
         <v>0</v>
       </c>
       <c r="C52" s="3">
-        <v>211041</v>
+        <v>211031</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3">
-        <v>3</v>
+        <v>89</v>
+      </c>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8">
+        <v>13</v>
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
-      <c r="J52" s="3"/>
+      <c r="J52" s="8" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A53" s="3" t="s">
@@ -2641,19 +2697,245 @@
         <v>0</v>
       </c>
       <c r="C53" s="3">
-        <v>211042</v>
+        <v>211032</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <v>3</v>
+      <c r="G53" s="8">
+        <v>13</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="3"/>
+    </row>
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A54" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3">
+        <v>211033</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="8">
+        <v>13</v>
+      </c>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="3"/>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A55" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C55" s="3">
+        <v>211034</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3">
+        <v>14</v>
+      </c>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A56" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3">
+        <v>211035</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3">
+        <v>14</v>
+      </c>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="3"/>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A57" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3">
+        <v>211036</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3">
+        <v>14</v>
+      </c>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="3"/>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A58" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3">
+        <v>211037</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3">
+        <v>10</v>
+      </c>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A59" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3">
+        <v>211038</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3">
+        <v>10</v>
+      </c>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="3"/>
+    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A60" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3">
+        <v>211039</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3">
+        <v>10</v>
+      </c>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="3"/>
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A61" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3">
+        <v>211040</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3">
+        <v>3</v>
+      </c>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A62" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3">
+        <v>211041</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3">
+        <v>3</v>
+      </c>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="3"/>
+    </row>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A63" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C63" s="3">
+        <v>211042</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3">
+        <v>3</v>
+      </c>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="106">
   <si>
     <t>#</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>Part</t>
   </si>
   <si>
     <t>AtrIdList</t>
@@ -1334,23 +1337,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.5" style="1" customWidth="1"/>
-    <col min="3" max="4" width="13" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.0833333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16" style="2" customWidth="1"/>
-    <col min="10" max="10" width="40.3333333333333" style="1" customWidth="1"/>
-    <col min="11" max="16372" width="13" style="1" customWidth="1"/>
-    <col min="16373" max="16384" width="13" style="1"/>
+    <col min="3" max="5" width="13" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.0833333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1666666666667" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="40.3333333333333" style="1" customWidth="1"/>
+    <col min="12" max="16373" width="13" style="1" customWidth="1"/>
+    <col min="16374" max="16384" width="13" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1358,13 +1361,14 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="2"/>
+      <c r="H1" s="3"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2"/>
+      <c r="K1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1372,13 +1376,14 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="2"/>
+      <c r="H2" s="3"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2"/>
+      <c r="K2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A3" s="4"/>
       <c r="B3" s="3"/>
       <c r="C3" s="5" t="s">
@@ -1387,7 +1392,7 @@
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="6" t="s">
@@ -1396,26 +1401,29 @@
       <c r="G3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K3" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A4" s="4"/>
       <c r="B4" s="3"/>
       <c r="C4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="6" t="s">
@@ -1424,1248 +1432,1390 @@
       <c r="G4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A5" s="4"/>
       <c r="B5" s="3"/>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="H5" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="I5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="5"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:10">
+        <v>15</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3">
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="3">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3">
         <v>28</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>10</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>1</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="I6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="2">
         <v>3</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="3">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3">
         <v>14</v>
       </c>
-      <c r="F7" s="3">
+      <c r="G7" s="3">
         <v>10</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>1</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="I7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="2">
         <v>3</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K7" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
         <v>1002</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>10</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="I8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="2">
         <v>3</v>
       </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3">
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="3">
+        <v>22</v>
+      </c>
+      <c r="E9" s="1">
+        <v>7</v>
+      </c>
+      <c r="F9" s="3">
         <v>85</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5</v>
       </c>
-      <c r="G9" s="3">
-        <f t="shared" ref="G9:G14" si="0">G6+1</f>
+      <c r="H9" s="3">
+        <f t="shared" ref="H9:H14" si="0">H6+1</f>
         <v>2</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="2">
+      <c r="I9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="2">
         <v>8</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K9" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3">
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="3">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
         <v>85</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="2">
+      <c r="I10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="2">
         <v>8</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K10" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3">
         <v>6</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="3">
+        <v>27</v>
+      </c>
+      <c r="E11" s="1">
+        <v>9</v>
+      </c>
+      <c r="F11" s="3">
         <v>85</v>
       </c>
-      <c r="F11" s="3">
+      <c r="G11" s="3">
         <v>5</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="2">
+      <c r="I11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="2">
         <v>8</v>
       </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
         <v>86</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="2">
+      <c r="I12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="2">
         <v>10</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K12" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" customHeight="1" spans="1:11">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3">
         <v>8</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="3">
+        <v>31</v>
+      </c>
+      <c r="E13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="3">
         <v>86</v>
       </c>
-      <c r="F13" s="3">
+      <c r="G13" s="3">
         <v>5</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13" s="2">
+      <c r="I13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="2">
         <v>10</v>
       </c>
-      <c r="J13" s="8"/>
-    </row>
-    <row r="14" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" customFormat="1" customHeight="1" spans="1:11">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="3">
+        <v>32</v>
+      </c>
+      <c r="E14" s="1">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3">
         <v>86</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14" s="2">
+      <c r="I14" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="2">
         <v>10</v>
       </c>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" customFormat="1" customHeight="1" spans="1:11">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3">
         <v>10</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="3">
+        <v>33</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3">
         <v>13</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4</v>
       </c>
-      <c r="H15" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I15" s="2">
+      <c r="I15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="2">
         <v>15</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K15" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="1:11">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3">
         <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="3">
+        <v>36</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3</v>
+      </c>
+      <c r="F16" s="3">
         <v>10</v>
       </c>
-      <c r="F16" s="3">
+      <c r="G16" s="3">
         <v>5</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>4</v>
       </c>
-      <c r="H16" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I16" s="2">
+      <c r="I16" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="2">
         <v>15</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K16" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" customHeight="1" spans="1:11">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3">
         <v>12</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="3">
+        <v>38</v>
+      </c>
+      <c r="E17" s="1">
+        <v>7</v>
+      </c>
+      <c r="F17" s="3">
         <v>11</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4</v>
       </c>
-      <c r="H17" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I17" s="2">
+      <c r="I17" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J17" s="2">
         <v>15</v>
       </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K17" s="3"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3">
         <v>13</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E18" s="3">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3">
         <v>2003</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5</v>
       </c>
-      <c r="H18" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I18" s="2">
+      <c r="I18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J18" s="2">
         <v>20</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K18" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3">
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="3">
+        <v>42</v>
+      </c>
+      <c r="E19" s="1">
+        <v>5</v>
+      </c>
+      <c r="F19" s="3">
         <v>2002</v>
       </c>
-      <c r="F19" s="3">
+      <c r="G19" s="3">
         <v>10</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>5</v>
       </c>
-      <c r="H19" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I19" s="2">
+      <c r="I19" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J19" s="2">
         <v>20</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K19" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="3">
+        <v>44</v>
+      </c>
+      <c r="E20" s="1">
+        <v>9</v>
+      </c>
+      <c r="F20" s="3">
         <v>2001</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5</v>
       </c>
-      <c r="H20" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I20" s="2">
+      <c r="I20" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J20" s="2">
         <v>20</v>
       </c>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="3">
+        <v>45</v>
+      </c>
+      <c r="E21" s="1">
+        <v>7</v>
+      </c>
+      <c r="F21" s="3">
         <v>21</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6</v>
       </c>
-      <c r="H21" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" s="2">
+      <c r="I21" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" s="2">
         <v>25</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K21" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E22" s="3">
+        <v>2</v>
+      </c>
+      <c r="F22" s="3">
         <v>22</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>20</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6</v>
       </c>
-      <c r="H22" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I22" s="2">
+      <c r="I22" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="2">
         <v>25</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K22" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A23" s="3"/>
       <c r="C23" s="3">
         <v>18</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23" s="3">
+        <v>50</v>
+      </c>
+      <c r="E23" s="1">
+        <v>10</v>
+      </c>
+      <c r="F23" s="3">
         <v>27</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6</v>
       </c>
-      <c r="H23" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I23" s="2">
+      <c r="I23" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" s="2">
         <v>25</v>
       </c>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K23" s="3"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A24" s="3"/>
       <c r="C24" s="3">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E24" s="3">
+        <v>51</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3">
         <v>23</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7</v>
       </c>
-      <c r="H24" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I24" s="2">
+      <c r="I24" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J24" s="2">
         <v>30</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K24" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A25" s="3"/>
       <c r="C25" s="3">
         <v>20</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="3">
+        <v>54</v>
+      </c>
+      <c r="E25" s="1">
+        <v>5</v>
+      </c>
+      <c r="F25" s="3">
         <v>24</v>
       </c>
-      <c r="F25" s="3">
+      <c r="G25" s="3">
         <v>30</v>
       </c>
-      <c r="G25" s="3">
+      <c r="H25" s="3">
         <v>7</v>
       </c>
-      <c r="H25" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I25" s="2">
+      <c r="I25" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J25" s="2">
         <v>30</v>
       </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K25" s="3"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3">
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26" s="3">
+        <v>55</v>
+      </c>
+      <c r="E26" s="1">
+        <v>7</v>
+      </c>
+      <c r="F26" s="3">
         <v>27</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7</v>
       </c>
-      <c r="H26" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I26" s="2">
+      <c r="I26" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="2">
         <v>30</v>
       </c>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3">
         <v>22</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
         <v>2003</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8</v>
       </c>
-      <c r="H27" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="I27" s="2">
+      <c r="I27" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J27" s="2">
         <v>35</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K27" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3">
         <v>23</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28" s="3">
+        <v>59</v>
+      </c>
+      <c r="E28" s="1">
+        <v>3</v>
+      </c>
+      <c r="F28" s="3">
         <v>27</v>
       </c>
-      <c r="F28" s="3">
+      <c r="G28" s="3">
         <v>15</v>
       </c>
-      <c r="G28" s="3">
+      <c r="H28" s="3">
         <v>8</v>
       </c>
-      <c r="H28" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" s="2">
+      <c r="I28" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J28" s="2">
         <v>35</v>
       </c>
-      <c r="J28" s="3"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K28" s="3"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="3">
+        <v>60</v>
+      </c>
+      <c r="E29" s="1">
+        <v>7</v>
+      </c>
+      <c r="F29" s="3">
         <v>13</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>15</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>8</v>
       </c>
-      <c r="H29" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="I29" s="2">
+      <c r="I29" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J29" s="2">
         <v>35</v>
       </c>
-      <c r="J29" s="3"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K29" s="3"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3">
         <v>25</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="3">
+        <v>61</v>
+      </c>
+      <c r="E30" s="1">
+        <v>4</v>
+      </c>
+      <c r="F30" s="3">
         <v>81</v>
       </c>
-      <c r="F30" s="3">
+      <c r="G30" s="3">
         <v>10</v>
       </c>
-      <c r="G30" s="3">
+      <c r="H30" s="3">
         <v>9</v>
       </c>
-      <c r="H30" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I30" s="2">
+      <c r="I30" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J30" s="2">
         <v>40</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K30" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3">
         <v>26</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" s="3">
+        <v>64</v>
+      </c>
+      <c r="E31" s="1">
+        <v>5</v>
+      </c>
+      <c r="F31" s="3">
         <v>83</v>
       </c>
-      <c r="F31" s="3">
+      <c r="G31" s="3">
         <v>5</v>
       </c>
-      <c r="G31" s="3">
+      <c r="H31" s="3">
         <v>9</v>
       </c>
-      <c r="H31" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I31" s="2">
+      <c r="I31" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J31" s="2">
         <v>40</v>
       </c>
-      <c r="J31" s="3"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K31" s="3"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E32" s="3">
+        <v>2</v>
+      </c>
+      <c r="F32" s="3">
         <v>82</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>10</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9</v>
       </c>
-      <c r="H32" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I32" s="2">
+      <c r="I32" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J32" s="2">
         <v>40</v>
       </c>
-      <c r="J32" s="3"/>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K32" s="3"/>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3">
         <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E33" s="3">
+        <v>66</v>
+      </c>
+      <c r="E33" s="1">
+        <v>7</v>
+      </c>
+      <c r="F33" s="3">
         <v>84</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10</v>
       </c>
-      <c r="H33" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I33" s="2">
+      <c r="I33" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J33" s="2">
         <v>45</v>
       </c>
-      <c r="J33" s="3"/>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K33" s="3"/>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3">
         <v>29</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E34" s="3">
+        <v>68</v>
+      </c>
+      <c r="E34" s="1">
+        <v>3</v>
+      </c>
+      <c r="F34" s="3">
         <v>81</v>
-      </c>
-      <c r="F34" s="3">
-        <v>10</v>
       </c>
       <c r="G34" s="3">
         <v>10</v>
       </c>
-      <c r="H34" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I34" s="2">
+      <c r="H34" s="3">
+        <v>10</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J34" s="2">
         <v>45</v>
       </c>
-      <c r="J34" s="3"/>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K34" s="3"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3">
         <v>30</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E35" s="3">
+        <v>69</v>
+      </c>
+      <c r="E35" s="1">
+        <v>9</v>
+      </c>
+      <c r="F35" s="3">
         <v>82</v>
-      </c>
-      <c r="F35" s="3">
-        <v>10</v>
       </c>
       <c r="G35" s="3">
         <v>10</v>
       </c>
-      <c r="H35" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I35" s="2">
+      <c r="H35" s="3">
+        <v>10</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J35" s="2">
         <v>45</v>
       </c>
-      <c r="J35" s="3"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:10">
+      <c r="K35" s="3"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:11">
       <c r="C36" s="3">
         <v>31</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E36" s="3">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3">
         <v>2003</v>
       </c>
-      <c r="F36" s="3">
+      <c r="G36" s="3">
         <v>20</v>
       </c>
-      <c r="G36" s="1">
+      <c r="H36" s="1">
         <v>11</v>
       </c>
-      <c r="H36" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I36" s="2">
+      <c r="I36" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="J36" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:10">
+    <row r="37" customHeight="1" spans="1:11">
       <c r="C37" s="3">
         <v>32</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E37" s="1">
+        <v>4</v>
+      </c>
+      <c r="F37" s="3">
+        <v>2002</v>
+      </c>
+      <c r="G37" s="3">
+        <v>20</v>
+      </c>
+      <c r="H37" s="1">
+        <v>11</v>
+      </c>
+      <c r="I37" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E37" s="3">
-        <v>2002</v>
-      </c>
-      <c r="F37" s="3">
-        <v>20</v>
-      </c>
-      <c r="G37" s="1">
-        <v>11</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I37" s="2">
+      <c r="J37" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="38" customFormat="1" customHeight="1" spans="1:10">
+    <row r="38" customFormat="1" customHeight="1" spans="1:11">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="3">
         <v>33</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E38" s="3">
+        <v>73</v>
+      </c>
+      <c r="E38" s="1">
+        <v>5</v>
+      </c>
+      <c r="F38" s="3">
         <v>2001</v>
       </c>
-      <c r="F38" s="3">
+      <c r="G38" s="3">
         <v>20</v>
       </c>
-      <c r="G38" s="1">
+      <c r="H38" s="1">
         <v>11</v>
       </c>
-      <c r="H38" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="I38" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="J38" s="2">
         <v>50</v>
       </c>
-      <c r="J38" s="1"/>
-    </row>
-    <row r="39" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K38" s="1"/>
+    </row>
+    <row r="39" customFormat="1" customHeight="1" spans="1:11">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="3">
         <v>34</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E39" s="3">
+        <v>2</v>
+      </c>
+      <c r="F39" s="3">
         <v>2003</v>
       </c>
-      <c r="F39" s="3">
+      <c r="G39" s="3">
         <v>25</v>
       </c>
-      <c r="G39" s="1">
+      <c r="H39" s="1">
         <v>12</v>
       </c>
-      <c r="H39" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I39" s="2">
+      <c r="I39" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J39" s="2">
         <v>55</v>
       </c>
-      <c r="J39" s="1"/>
-    </row>
-    <row r="40" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K39" s="1"/>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="1:11">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="3">
         <v>35</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E40" s="1">
+        <v>7</v>
+      </c>
+      <c r="F40" s="3">
+        <v>2002</v>
+      </c>
+      <c r="G40" s="3">
+        <v>25</v>
+      </c>
+      <c r="H40" s="1">
+        <v>12</v>
+      </c>
+      <c r="I40" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E40" s="3">
-        <v>2002</v>
-      </c>
-      <c r="F40" s="3">
-        <v>25</v>
-      </c>
-      <c r="G40" s="1">
-        <v>12</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I40" s="2">
+      <c r="J40" s="2">
         <v>55</v>
       </c>
-      <c r="J40" s="1"/>
-    </row>
-    <row r="41" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K40" s="1"/>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="1:11">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="3">
         <v>36</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E41" s="3">
+        <v>77</v>
+      </c>
+      <c r="E41" s="1">
+        <v>10</v>
+      </c>
+      <c r="F41" s="3">
         <v>2001</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25</v>
       </c>
-      <c r="G41" s="1">
+      <c r="H41" s="1">
         <v>12</v>
       </c>
-      <c r="H41" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I41" s="2">
+      <c r="I41" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J41" s="2">
         <v>55</v>
       </c>
-      <c r="J41" s="1"/>
-    </row>
-    <row r="42" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K41" s="1"/>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="1:11">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="3">
         <v>37</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E42" s="3">
+        <v>78</v>
+      </c>
+      <c r="E42" s="1">
+        <v>4</v>
+      </c>
+      <c r="F42" s="3">
         <v>2003</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>30</v>
       </c>
-      <c r="G42" s="1">
+      <c r="H42" s="1">
         <v>13</v>
       </c>
-      <c r="H42" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I42" s="2">
+      <c r="I42" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="J42" s="2">
         <v>60</v>
       </c>
-      <c r="J42" s="1"/>
-    </row>
-    <row r="43" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K42" s="1"/>
+    </row>
+    <row r="43" customFormat="1" customHeight="1" spans="1:11">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="3">
         <v>38</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43" s="1">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3">
+        <v>2002</v>
+      </c>
+      <c r="G43" s="3">
+        <v>30</v>
+      </c>
+      <c r="H43" s="1">
+        <v>13</v>
+      </c>
+      <c r="I43" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E43" s="3">
-        <v>2002</v>
-      </c>
-      <c r="F43" s="3">
-        <v>30</v>
-      </c>
-      <c r="G43" s="1">
-        <v>13</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I43" s="2">
+      <c r="J43" s="2">
         <v>60</v>
       </c>
-      <c r="J43" s="1"/>
-    </row>
-    <row r="44" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K43" s="1"/>
+    </row>
+    <row r="44" customFormat="1" customHeight="1" spans="1:11">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="3">
         <v>39</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E44" s="3">
+        <v>2</v>
+      </c>
+      <c r="F44" s="3">
         <v>2001</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>30</v>
       </c>
-      <c r="G44" s="1">
+      <c r="H44" s="1">
         <v>13</v>
       </c>
-      <c r="H44" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I44" s="2">
+      <c r="I44" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="J44" s="2">
         <v>60</v>
       </c>
-      <c r="J44" s="1"/>
-    </row>
-    <row r="45" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K44" s="1"/>
+    </row>
+    <row r="45" customFormat="1" customHeight="1" spans="1:11">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="3">
         <v>40</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E45" s="3">
+        <v>2</v>
+      </c>
+      <c r="F45" s="3">
         <v>2003</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>35</v>
       </c>
-      <c r="G45" s="1">
+      <c r="H45" s="1">
         <v>14</v>
       </c>
-      <c r="H45" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I45" s="2">
+      <c r="I45" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J45" s="2">
         <v>80</v>
       </c>
-      <c r="J45" s="1"/>
-    </row>
-    <row r="46" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K45" s="1"/>
+    </row>
+    <row r="46" customFormat="1" customHeight="1" spans="1:11">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="3">
         <v>41</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E46" s="1">
+        <v>9</v>
+      </c>
+      <c r="F46" s="3">
+        <v>2002</v>
+      </c>
+      <c r="G46" s="3">
+        <v>35</v>
+      </c>
+      <c r="H46" s="1">
+        <v>14</v>
+      </c>
+      <c r="I46" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E46" s="3">
-        <v>2002</v>
-      </c>
-      <c r="F46" s="3">
-        <v>35</v>
-      </c>
-      <c r="G46" s="1">
-        <v>14</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I46" s="2">
+      <c r="J46" s="2">
         <v>80</v>
       </c>
-      <c r="J46" s="1"/>
-    </row>
-    <row r="47" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K46" s="1"/>
+    </row>
+    <row r="47" customFormat="1" customHeight="1" spans="1:11">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="3">
         <v>42</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E47" s="3">
+        <v>85</v>
+      </c>
+      <c r="E47" s="1">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3">
         <v>2001</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>35</v>
       </c>
-      <c r="G47" s="1">
+      <c r="H47" s="1">
         <v>14</v>
       </c>
-      <c r="H47" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I47" s="2">
+      <c r="I47" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J47" s="2">
         <v>80</v>
       </c>
-      <c r="J47" s="1"/>
-    </row>
-    <row r="48" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K47" s="1"/>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="1:11">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="3">
         <v>43</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E48" s="3">
+        <v>2</v>
+      </c>
+      <c r="F48" s="3">
         <v>2003</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>40</v>
       </c>
-      <c r="G48" s="1">
+      <c r="H48" s="1">
         <v>15</v>
       </c>
-      <c r="H48" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I48" s="2">
+      <c r="I48" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J48" s="2">
         <v>100</v>
       </c>
-      <c r="J48" s="1"/>
-    </row>
-    <row r="49" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K48" s="1"/>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="1:11">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="3">
         <v>44</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E49" s="1">
+        <v>7</v>
+      </c>
+      <c r="F49" s="3">
+        <v>2002</v>
+      </c>
+      <c r="G49" s="3">
+        <v>40</v>
+      </c>
+      <c r="H49" s="1">
+        <v>15</v>
+      </c>
+      <c r="I49" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E49" s="3">
-        <v>2002</v>
-      </c>
-      <c r="F49" s="3">
-        <v>40</v>
-      </c>
-      <c r="G49" s="1">
-        <v>15</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I49" s="2">
+      <c r="J49" s="2">
         <v>100</v>
       </c>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K49" s="1"/>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="1:11">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="3">
         <v>45</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E50" s="3">
+        <v>89</v>
+      </c>
+      <c r="E50" s="1">
+        <v>9</v>
+      </c>
+      <c r="F50" s="3">
         <v>2001</v>
       </c>
-      <c r="F50" s="3">
+      <c r="G50" s="3">
         <v>40</v>
       </c>
-      <c r="G50" s="1">
+      <c r="H50" s="1">
         <v>15</v>
       </c>
-      <c r="H50" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I50" s="2">
+      <c r="I50" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J50" s="2">
         <v>100</v>
       </c>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K50" s="1"/>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="1:11">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="3"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="3"/>
+      <c r="E51" s="1"/>
       <c r="F51" s="3"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="2"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="1"/>
       <c r="I51" s="2"/>
-      <c r="J51" s="1"/>
-    </row>
-    <row r="52" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J51" s="2"/>
+      <c r="K51" s="1"/>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="1:11">
       <c r="A52" s="3" t="s">
         <v>0</v>
       </c>
@@ -2676,20 +2826,21 @@
         <v>211031</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E52" s="8"/>
+        <v>90</v>
+      </c>
+      <c r="E52" s="3"/>
       <c r="F52" s="8"/>
-      <c r="G52" s="8">
+      <c r="G52" s="8"/>
+      <c r="H52" s="8">
         <v>13</v>
       </c>
-      <c r="H52" s="2"/>
       <c r="I52" s="2"/>
-      <c r="J52" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J52" s="2"/>
+      <c r="K52" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A53" s="3" t="s">
         <v>0</v>
       </c>
@@ -2700,18 +2851,19 @@
         <v>211032</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
-      <c r="G53" s="8">
+      <c r="G53" s="3"/>
+      <c r="H53" s="8">
         <v>13</v>
       </c>
-      <c r="H53" s="2"/>
       <c r="I53" s="2"/>
-      <c r="J53" s="3"/>
-    </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J53" s="2"/>
+      <c r="K53" s="3"/>
+    </row>
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A54" s="3" t="s">
         <v>0</v>
       </c>
@@ -2722,18 +2874,19 @@
         <v>211033</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
-      <c r="G54" s="8">
+      <c r="G54" s="3"/>
+      <c r="H54" s="8">
         <v>13</v>
       </c>
-      <c r="H54" s="2"/>
       <c r="I54" s="2"/>
-      <c r="J54" s="3"/>
-    </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J54" s="2"/>
+      <c r="K54" s="3"/>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A55" s="3" t="s">
         <v>0</v>
       </c>
@@ -2744,20 +2897,21 @@
         <v>211034</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
-      <c r="G55" s="3">
+      <c r="G55" s="3"/>
+      <c r="H55" s="3">
         <v>14</v>
       </c>
-      <c r="H55" s="2"/>
       <c r="I55" s="2"/>
-      <c r="J55" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J55" s="2"/>
+      <c r="K55" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A56" s="3" t="s">
         <v>0</v>
       </c>
@@ -2768,18 +2922,19 @@
         <v>211035</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
-      <c r="G56" s="3">
+      <c r="G56" s="3"/>
+      <c r="H56" s="3">
         <v>14</v>
       </c>
-      <c r="H56" s="2"/>
       <c r="I56" s="2"/>
-      <c r="J56" s="3"/>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J56" s="2"/>
+      <c r="K56" s="3"/>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A57" s="3" t="s">
         <v>0</v>
       </c>
@@ -2790,18 +2945,19 @@
         <v>211036</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
-      <c r="G57" s="3">
+      <c r="G57" s="3"/>
+      <c r="H57" s="3">
         <v>14</v>
       </c>
-      <c r="H57" s="2"/>
       <c r="I57" s="2"/>
-      <c r="J57" s="3"/>
-    </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J57" s="2"/>
+      <c r="K57" s="3"/>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A58" s="3" t="s">
         <v>0</v>
       </c>
@@ -2812,20 +2968,21 @@
         <v>211037</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="3">
+      <c r="G58" s="3"/>
+      <c r="H58" s="3">
         <v>10</v>
       </c>
-      <c r="H58" s="2"/>
       <c r="I58" s="2"/>
-      <c r="J58" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J58" s="2"/>
+      <c r="K58" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A59" s="3" t="s">
         <v>0</v>
       </c>
@@ -2836,18 +2993,19 @@
         <v>211038</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
-      <c r="G59" s="3">
+      <c r="G59" s="3"/>
+      <c r="H59" s="3">
         <v>10</v>
       </c>
-      <c r="H59" s="2"/>
       <c r="I59" s="2"/>
-      <c r="J59" s="3"/>
-    </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J59" s="2"/>
+      <c r="K59" s="3"/>
+    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A60" s="3" t="s">
         <v>0</v>
       </c>
@@ -2858,18 +3016,19 @@
         <v>211039</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
-      <c r="G60" s="3">
+      <c r="G60" s="3"/>
+      <c r="H60" s="3">
         <v>10</v>
       </c>
-      <c r="H60" s="2"/>
       <c r="I60" s="2"/>
-      <c r="J60" s="3"/>
-    </row>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J60" s="2"/>
+      <c r="K60" s="3"/>
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A61" s="3" t="s">
         <v>0</v>
       </c>
@@ -2880,20 +3039,21 @@
         <v>211040</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
-      <c r="G61" s="3">
+      <c r="G61" s="3"/>
+      <c r="H61" s="3">
         <v>3</v>
       </c>
-      <c r="H61" s="2"/>
       <c r="I61" s="2"/>
-      <c r="J61" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J61" s="2"/>
+      <c r="K61" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A62" s="3" t="s">
         <v>0</v>
       </c>
@@ -2904,18 +3064,19 @@
         <v>211041</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
-      <c r="G62" s="3">
+      <c r="G62" s="3"/>
+      <c r="H62" s="3">
         <v>3</v>
       </c>
-      <c r="H62" s="2"/>
       <c r="I62" s="2"/>
-      <c r="J62" s="3"/>
-    </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J62" s="2"/>
+      <c r="K62" s="3"/>
+    </row>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A63" s="3" t="s">
         <v>0</v>
       </c>
@@ -2926,20 +3087,21 @@
         <v>211042</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
-      <c r="G63" s="3">
+      <c r="G63" s="3"/>
+      <c r="H63" s="3">
         <v>3</v>
       </c>
-      <c r="H63" s="2"/>
       <c r="I63" s="2"/>
-      <c r="J63" s="3"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3:J5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:E5 K3:K5 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -295,7 +295,7 @@
     <t>冰霜项链</t>
   </si>
   <si>
-    <t>5E+9</t>
+    <t>2E+9</t>
   </si>
   <si>
     <t>冰霜戒指</t>
@@ -3101,7 +3101,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:E5 K3:K5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3:K5 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
